--- a/outputs/A11derived_v18.xlsx
+++ b/outputs/A11derived_v18.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表b：T11 CI 宽度与比值" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表c：R2 分母口径之比" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表d：猕猴桃掩膜空操作核验" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表e：衰减比两口径" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,68 +664,94 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>两口径之差·逐次最大（全精度）</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>重放划分次数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>折算依据</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>猕猴桃 DM</t>
+          <t>猕猴桃 DM（T10）</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.827</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9990696182577574</v>
+        <v>0.9990054240132292</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9927919794904879</v>
+        <v>0.9954904825011279</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8268388940685748</v>
+        <v>0.826827767055538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001611059314251539</v>
+        <v>0.000172232944462003</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>0.0007836805484516298</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>报告值 × ρ 均值折算；划分与 T10 实跑的 5×6=30 次逐一相同</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>猕猴桃 SSC</t>
+          <t>猕猴桃 SSC（T10）</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.861</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9990459341010283</v>
+        <v>0.9987985530404748</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9931862206911214</v>
+        <v>0.9937438582846911</v>
       </c>
       <c r="E3" t="n">
-        <v>0.860867258195614</v>
+        <v>0.8608327979882774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001327418043859385</v>
+        <v>0.0001672020117226003</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>0.000875078312362076</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>报告值 × ρ 均值折算；划分与 T10 实跑的 5×6=30 次逐一相同</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>苹果 SSC</t>
+          <t>苹果 面级 SSC（主表 raw）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.82</v>
+        <v>0.06651739616571645</v>
       </c>
       <c r="C4" t="n">
         <v>0.9961897192964591</v>
@@ -733,13 +760,54 @@
         <v>0.9639878707284368</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8193115261949082</v>
+        <v>0.06294827594016476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006884738050917383</v>
+        <v>0.003569120225551672</v>
       </c>
       <c r="G4" t="n">
+        <v>0.03299057100145764</v>
+      </c>
+      <c r="H4" t="n">
         <v>100</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>逐次折算：A4formal_v18_raw.json 主表 raw 的 100 次 R² × 同序重放的逐次 ρ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>苹果 整果均值 SSC（主表 raw）</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.118012728534467</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9935050439061222</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9383993608947444</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1121703086061703</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005842419928296736</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05456651636861642</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>逐次折算：A4formal_v18_raw.json 主表 raw 的 100 次 R² × 同序重放的逐次 ρ</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -823,4 +891,109 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>口径</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>衰减比 = R²(面级)/R²(整果均值)（均值之比）</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>cluster CI95 下限</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>cluster CI95 上限</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>含理论值 0.5816</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>排除 ICC 0.477</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>训练均值口径（正文口径）</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5636459472783841</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5307499409799468</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5961525488620713</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>须逐位复现 A5 表b（同一逐次 R²、同一自助算法与种子）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>测试均值口径</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.5611848333338909</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5263140029476282</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5952654785635446</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>同一划分、同一逐次 R² 折算到测试均值口径后重算；两条判定均须与正文口径一致</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>